--- a/artfynd/A 30411-2022 artfynd.xlsx
+++ b/artfynd/A 30411-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30411-2022 artfynd.xlsx
+++ b/artfynd/A 30411-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4292,6 +4292,112 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120440246</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fänisvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>434312</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7017287</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2017-01-31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2018-12-31</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventering Nya Komet 2017-2018</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
